--- a/apps/isomorphic/public/templates/events.xlsx
+++ b/apps/isomorphic/public/templates/events.xlsx
@@ -28,54 +28,150 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>eventName</t>
-  </si>
-  <si>
-    <t>clientName</t>
-  </si>
-  <si>
-    <t>startDate</t>
-  </si>
-  <si>
-    <t>endDate</t>
-  </si>
-  <si>
-    <t>Annual Tech Conference 2026</t>
-  </si>
-  <si>
-    <t>FleetStakes Pvt Ltd</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>2026-04-12</t>
-  </si>
-  <si>
-    <t>elementName</t>
-  </si>
-  <si>
-    <t>quantity</t>
-  </si>
-  <si>
-    <t>Stage Setup</t>
-  </si>
-  <si>
-    <t>LED Screen</t>
-  </si>
-  <si>
-    <t>Sound System</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+  <si>
+    <t>EVENT DETAILS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>EVENT Name</t>
+  </si>
+  <si>
+    <t>Cardio Annual Summit Brochure</t>
+  </si>
+  <si>
+    <t>Job No</t>
+  </si>
+  <si>
+    <t>KJ/JAN/25-26/0001</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Intas</t>
+  </si>
+  <si>
+    <t>Event Type</t>
+  </si>
+  <si>
+    <t>Conference</t>
+  </si>
+  <si>
+    <t>Event Date</t>
+  </si>
+  <si>
+    <t>2026-01-15 - 2026-01-17</t>
+  </si>
+  <si>
+    <t>Divisions</t>
+  </si>
+  <si>
+    <t>SAP Code</t>
+  </si>
+  <si>
+    <t>Altis</t>
+  </si>
+  <si>
+    <t>Arron</t>
+  </si>
+  <si>
+    <t>Elements</t>
+  </si>
+  <si>
+    <t>sr.</t>
+  </si>
+  <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Depth</t>
+  </si>
+  <si>
+    <t>unit type</t>
+  </si>
+  <si>
+    <t>Sqft</t>
+  </si>
+  <si>
+    <t>sqft Rate</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <t>Chair</t>
   </si>
   <si>
-    <t>Projector</t>
-  </si>
-  <si>
-    <t>Projector Screen</t>
+    <t>perpcs</t>
+  </si>
+  <si>
+    <t>Stall</t>
+  </si>
+  <si>
+    <t>persqft</t>
+  </si>
+  <si>
+    <t>FINAL QUOTE</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>GST %</t>
+  </si>
+  <si>
+    <t>Freight</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Delivery Time</t>
+  </si>
+  <si>
+    <t>Validity</t>
+  </si>
+  <si>
+    <t>Vendor Name</t>
+  </si>
+  <si>
+    <t>Authorized Sign</t>
+  </si>
+  <si>
+    <t>Terms And Condition</t>
+  </si>
+  <si>
+    <t>Vendor must share per sq. ft. rate in rate column</t>
+  </si>
+  <si>
+    <t>Vendor cannot add/delete items from element sheet</t>
+  </si>
+  <si>
+    <t>Revised sheet will be shared for any changes</t>
+  </si>
+  <si>
+    <t>No advance will be released</t>
+  </si>
+  <si>
+    <t>PO will be released within one week prior to event</t>
   </si>
 </sst>
 </file>
@@ -88,7 +184,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,17 +195,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF484848"/>
+      <name val="Inter"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -256,7 +356,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -265,12 +365,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -456,27 +550,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -580,156 +659,159 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1076,96 +1158,285 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.8888888888889" customWidth="1"/>
-    <col min="2" max="2" width="17.7777777777778" customWidth="1"/>
-    <col min="3" max="4" width="11.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="49.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="5.55555555555556" customWidth="1"/>
+    <col min="4" max="4" width="4.55555555555556" customWidth="1"/>
+    <col min="5" max="5" width="6.55555555555556" customWidth="1"/>
+    <col min="6" max="6" width="7.11111111111111" customWidth="1"/>
+    <col min="7" max="7" width="6.88888888888889" customWidth="1"/>
+    <col min="8" max="8" width="6.55555555555556" customWidth="1"/>
+    <col min="9" max="9" width="8.57407407407407" customWidth="1"/>
+    <col min="10" max="10" width="6.66666666666667" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2">
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3">
+        <v>123456</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="I14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3">
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3">
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
